--- a/data/trans_orig/P1425-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1425-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2007</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39262</t>
+          <t>38870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36523</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39677</t>
+          <t>40452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67571</t>
+          <t>68801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>992461</t>
+          <t>992853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1012539</t>
+          <t>1013915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1278590</t>
+          <t>1279215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1298925</t>
+          <t>1298829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2279264</t>
+          <t>2278034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2307158</t>
+          <t>2306383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25921</t>
+          <t>25298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1677030</t>
+          <t>1676022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1689694</t>
+          <t>1689398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1573325</t>
+          <t>1574508</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1584629</t>
+          <t>1584647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3255165</t>
+          <t>3255788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3271716</t>
+          <t>3271917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11951</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539457</t>
+          <t>540934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549592</t>
+          <t>549635</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465798</t>
+          <t>465882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474548</t>
+          <t>474524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1010677</t>
+          <t>1011240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1023109</t>
+          <t>1022987</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54004</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,82 +1776,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>36848</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24563</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50002</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>77580</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>61383</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>97777</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36848</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26157</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>50834</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>77580</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>61588</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>95599</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3222539</t>
+          <t>3222225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3246442</t>
+          <t>3246849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,82 +1889,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3261</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3342349</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3329195</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3354634</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6434</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6578161</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6557964</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6594358</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3261</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3342349</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3328363</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3353040</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6434</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6578161</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6560142</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6594153</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2012</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>30895</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>22966</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>22557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47091</t>
+          <t>46869</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>943821</t>
+          <t>943748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>962737</t>
+          <t>963285</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1314584</t>
+          <t>1314831</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1329402</t>
+          <t>1330347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2265349</t>
+          <t>2265571</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2289779</t>
+          <t>2289883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17620</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23331</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1946337</t>
+          <t>1946810</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1960049</t>
+          <t>1959996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1742764</t>
+          <t>1741852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1753439</t>
+          <t>1753542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3695218</t>
+          <t>3695627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3711661</t>
+          <t>3712307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>13939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,39 +3036,39 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1780</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8842</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1780</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8898</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16579</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465973</t>
+          <t>467242</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479308</t>
+          <t>480038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,42 +3149,42 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>456851</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>449789</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>458631</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>99,61%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>456851</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>449733</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>458631</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>923234</t>
+          <t>922850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937622</t>
+          <t>937753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48519</t>
+          <t>48183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32020</t>
+          <t>32660</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37128</t>
+          <t>38666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69513</t>
+          <t>70385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3371263</t>
+          <t>3371599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3398416</t>
+          <t>3397858</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3519000</t>
+          <t>3518360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3538688</t>
+          <t>3539300</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6901288</t>
+          <t>6900416</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6933673</t>
+          <t>6932135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2016</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17891</t>
+          <t>19366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29527</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18739</t>
+          <t>19420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40370</t>
+          <t>40961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>736456</t>
+          <t>734981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>965133</t>
+          <t>967321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>985049</t>
+          <t>984821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1708637</t>
+          <t>1708046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1730268</t>
+          <t>1729587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27983</t>
+          <t>27976</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>24856</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45467</t>
+          <t>45236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2048402</t>
+          <t>2048409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2065617</t>
+          <t>2065712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1963275</t>
+          <t>1963444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1980805</t>
+          <t>1980399</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4019218</t>
+          <t>4019449</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4042648</t>
+          <t>4043163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538448</t>
+          <t>537804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542128</t>
+          <t>542000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1082944</t>
+          <t>1083818</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1094989</t>
+          <t>1095029</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22085</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45527</t>
+          <t>45384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>22729</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48419</t>
+          <t>47424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50061</t>
+          <t>49292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86496</t>
+          <t>84015</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3332091</t>
+          <t>3332234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3355533</t>
+          <t>3355367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3483681</t>
+          <t>3484676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3509196</t>
+          <t>3509371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6823222</t>
+          <t>6825703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6859657</t>
+          <t>6860426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1425-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1425-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38870</t>
+          <t>39945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35898</t>
+          <t>37020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40452</t>
+          <t>39588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68801</t>
+          <t>67318</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>992853</t>
+          <t>991778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1013915</t>
+          <t>1013549</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1279215</t>
+          <t>1278093</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1298829</t>
+          <t>1299603</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2278034</t>
+          <t>2279517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2306383</t>
+          <t>2307247</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1676022</t>
+          <t>1676382</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1689398</t>
+          <t>1689559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1574508</t>
+          <t>1573063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1584647</t>
+          <t>1584588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3255788</t>
+          <t>3255437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3271917</t>
+          <t>3271803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540934</t>
+          <t>540333</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549635</t>
+          <t>549629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465882</t>
+          <t>465477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474524</t>
+          <t>474526</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1011240</t>
+          <t>1010436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1022987</t>
+          <t>1023142</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29694</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>53903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50002</t>
+          <t>51608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61383</t>
+          <t>62951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97777</t>
+          <t>96573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3222225</t>
+          <t>3222640</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3246849</t>
+          <t>3247132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3329195</t>
+          <t>3327589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3354634</t>
+          <t>3353028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6557964</t>
+          <t>6559168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6594358</t>
+          <t>6592790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30895</t>
+          <t>31430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22557</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46869</t>
+          <t>47650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>943748</t>
+          <t>943213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>963285</t>
+          <t>962777</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1314831</t>
+          <t>1314606</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1330347</t>
+          <t>1330428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2265571</t>
+          <t>2264790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2289883</t>
+          <t>2289495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>11306</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1946810</t>
+          <t>1945421</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1959996</t>
+          <t>1960725</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1741852</t>
+          <t>1743286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1753542</t>
+          <t>1753444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3695627</t>
+          <t>3694249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3712307</t>
+          <t>3711789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16963</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>467242</t>
+          <t>466802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480038</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449789</t>
+          <t>449209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>922850</t>
+          <t>923567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937753</t>
+          <t>937738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48183</t>
+          <t>46423</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32660</t>
+          <t>31465</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38666</t>
+          <t>39425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70385</t>
+          <t>71642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3371599</t>
+          <t>3373359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3397858</t>
+          <t>3398455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3518360</t>
+          <t>3519555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3539300</t>
+          <t>3539392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6900416</t>
+          <t>6899159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6932135</t>
+          <t>6931376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40961</t>
+          <t>39836</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>734981</t>
+          <t>736251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748789</t>
+          <t>748439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>967321</t>
+          <t>966484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>984821</t>
+          <t>984337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1708046</t>
+          <t>1709171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1729587</t>
+          <t>1730417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27976</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>24929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21522</t>
+          <t>22235</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45236</t>
+          <t>46512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2048409</t>
+          <t>2049065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2065712</t>
+          <t>2065743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1963444</t>
+          <t>1963371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1980399</t>
+          <t>1980835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4019449</t>
+          <t>4018173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4043163</t>
+          <t>4042450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>13228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>537804</t>
+          <t>537076</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542000</t>
+          <t>542019</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1083818</t>
+          <t>1082799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1095029</t>
+          <t>1094980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45384</t>
+          <t>44159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22729</t>
+          <t>22025</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47424</t>
+          <t>48929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49292</t>
+          <t>50695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84015</t>
+          <t>84036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3332234</t>
+          <t>3333459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3355367</t>
+          <t>3356085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3484676</t>
+          <t>3483171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3509371</t>
+          <t>3510075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6825703</t>
+          <t>6825682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6860426</t>
+          <t>6859023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
